--- a/data/2026-05-02/BallparkPal_Pitchers.xlsx
+++ b/data/2026-05-02/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="124">
   <si>
     <t>GamePk</t>
   </si>
@@ -122,6 +122,30 @@
     <t>A</t>
   </si>
   <si>
+    <t>6:10</t>
+  </si>
+  <si>
+    <t>Griffin Jax</t>
+  </si>
+  <si>
+    <t>Jax</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>Landen Roupp</t>
+  </si>
+  <si>
+    <t>Roupp</t>
+  </si>
+  <si>
     <t>7:15</t>
   </si>
   <si>
@@ -131,9 +155,6 @@
     <t>McGreevy</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>STL</t>
   </si>
   <si>
@@ -206,6 +227,27 @@
     <t>Lowder</t>
   </si>
   <si>
+    <t>1:35</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>Weathers</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>Kyle Bradish</t>
+  </si>
+  <si>
+    <t>Bradish</t>
+  </si>
+  <si>
     <t>2:10</t>
   </si>
   <si>
@@ -242,6 +284,12 @@
     <t>PHI</t>
   </si>
   <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Painter</t>
+  </si>
+  <si>
     <t>9:38</t>
   </si>
   <si>
@@ -281,6 +329,27 @@
     <t>Rocker</t>
   </si>
   <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>Chris Sale</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Chase Dollander</t>
+  </si>
+  <si>
+    <t>Dollander</t>
+  </si>
+  <si>
     <t>2:20</t>
   </si>
   <si>
@@ -318,24 +387,6 @@
   </si>
   <si>
     <t>Early</t>
-  </si>
-  <si>
-    <t>Slade Cecconi</t>
-  </si>
-  <si>
-    <t>Cecconi</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>ATH</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Lopez</t>
   </si>
 </sst>
 </file>
@@ -675,7 +726,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -784,46 +835,46 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>19.566</v>
+        <v>19.472</v>
       </c>
       <c r="L2">
-        <v>4.548</v>
+        <v>4.533</v>
       </c>
       <c r="M2">
-        <v>0.17</v>
+        <v>0.177</v>
       </c>
       <c r="N2">
-        <v>0.299</v>
+        <v>0.297</v>
       </c>
       <c r="O2">
-        <v>0.531</v>
+        <v>0.526</v>
       </c>
       <c r="P2">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="Q2">
-        <v>11.468</v>
+        <v>11.627</v>
       </c>
       <c r="R2">
-        <v>21.536</v>
+        <v>21.748</v>
       </c>
       <c r="S2">
-        <v>1.909</v>
+        <v>1.913</v>
       </c>
       <c r="T2">
-        <v>4.173</v>
+        <v>4.146</v>
       </c>
       <c r="U2">
-        <v>4.036</v>
+        <v>4.113</v>
       </c>
       <c r="V2">
-        <v>1.994</v>
+        <v>1.992</v>
       </c>
       <c r="W2">
-        <v>0.381</v>
+        <v>0.353</v>
       </c>
       <c r="X2">
-        <v>0.759</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -858,51 +909,51 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>21.486</v>
+        <v>21.745</v>
       </c>
       <c r="L3">
-        <v>4.996</v>
+        <v>5.075</v>
       </c>
       <c r="M3">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="N3">
-        <v>0.273</v>
+        <v>0.288</v>
       </c>
       <c r="O3">
-        <v>0.534</v>
+        <v>0.517</v>
       </c>
       <c r="P3">
-        <v>0.264</v>
+        <v>0.286</v>
       </c>
       <c r="Q3">
-        <v>15.107</v>
+        <v>15.465</v>
       </c>
       <c r="R3">
-        <v>27.873</v>
+        <v>28.489</v>
       </c>
       <c r="S3">
-        <v>2.174</v>
+        <v>2.196</v>
       </c>
       <c r="T3">
-        <v>4.609</v>
+        <v>4.596</v>
       </c>
       <c r="U3">
-        <v>5.73</v>
+        <v>5.848</v>
       </c>
       <c r="V3">
-        <v>2.099</v>
+        <v>2.132</v>
       </c>
       <c r="W3">
-        <v>0.479</v>
+        <v>0.457</v>
       </c>
       <c r="X3">
-        <v>1.169</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4">
-        <v>823067</v>
+        <v>822988</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -911,7 +962,7 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>700241</v>
+        <v>643377</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -932,51 +983,51 @@
         <v>40</v>
       </c>
       <c r="K4">
-        <v>23.473</v>
+        <v>6.416</v>
       </c>
       <c r="L4">
-        <v>5.549</v>
+        <v>1.543</v>
       </c>
       <c r="M4">
-        <v>0.252</v>
+        <v>0.001</v>
       </c>
       <c r="N4">
-        <v>0.382</v>
+        <v>0.178</v>
       </c>
       <c r="O4">
-        <v>0.366</v>
+        <v>0.821</v>
       </c>
       <c r="P4">
-        <v>0.406</v>
+        <v>0.0</v>
       </c>
       <c r="Q4">
-        <v>11.62</v>
+        <v>5.083</v>
       </c>
       <c r="R4">
-        <v>23.301</v>
+        <v>8.673</v>
       </c>
       <c r="S4">
-        <v>2.42</v>
+        <v>0.519</v>
       </c>
       <c r="T4">
-        <v>5.144</v>
+        <v>1.327</v>
       </c>
       <c r="U4">
-        <v>3.592</v>
+        <v>1.864</v>
       </c>
       <c r="V4">
-        <v>1.928</v>
+        <v>0.479</v>
       </c>
       <c r="W4">
-        <v>0.627</v>
+        <v>0.197</v>
       </c>
       <c r="X4">
-        <v>0.416</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5">
-        <v>823067</v>
+        <v>822988</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -985,7 +1036,7 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>808963</v>
+        <v>694738</v>
       </c>
       <c r="E5" t="s">
         <v>41</v>
@@ -1006,51 +1057,51 @@
         <v>39</v>
       </c>
       <c r="K5">
-        <v>18.703</v>
+        <v>22.499</v>
       </c>
       <c r="L5">
-        <v>4.363</v>
+        <v>5.406</v>
       </c>
       <c r="M5">
-        <v>0.123</v>
+        <v>0.266</v>
       </c>
       <c r="N5">
-        <v>0.244</v>
+        <v>0.235</v>
       </c>
       <c r="O5">
-        <v>0.633</v>
+        <v>0.498</v>
       </c>
       <c r="P5">
-        <v>0.069</v>
+        <v>0.408</v>
       </c>
       <c r="Q5">
-        <v>10.148</v>
+        <v>16.155</v>
       </c>
       <c r="R5">
-        <v>19.109</v>
+        <v>29.716</v>
       </c>
       <c r="S5">
-        <v>1.785</v>
+        <v>1.855</v>
       </c>
       <c r="T5">
-        <v>3.472</v>
+        <v>3.993</v>
       </c>
       <c r="U5">
-        <v>3.454</v>
+        <v>5.278</v>
       </c>
       <c r="V5">
-        <v>2.357</v>
+        <v>2.561</v>
       </c>
       <c r="W5">
-        <v>0.348</v>
+        <v>0.379</v>
       </c>
       <c r="X5">
-        <v>0.4</v>
+        <v>0.568</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6">
-        <v>823144</v>
+        <v>823067</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1059,7 +1110,7 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>607625</v>
+        <v>700241</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
@@ -1071,7 +1122,7 @@
         <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
         <v>46</v>
@@ -1080,51 +1131,51 @@
         <v>47</v>
       </c>
       <c r="K6">
-        <v>23.036</v>
+        <v>23.418</v>
       </c>
       <c r="L6">
-        <v>5.364</v>
+        <v>5.479</v>
       </c>
       <c r="M6">
-        <v>0.163</v>
+        <v>0.237</v>
       </c>
       <c r="N6">
-        <v>0.428</v>
+        <v>0.383</v>
       </c>
       <c r="O6">
-        <v>0.409</v>
+        <v>0.379</v>
       </c>
       <c r="P6">
-        <v>0.358</v>
+        <v>0.373</v>
       </c>
       <c r="Q6">
-        <v>12.998</v>
+        <v>10.856</v>
       </c>
       <c r="R6">
-        <v>25.307</v>
+        <v>22.19</v>
       </c>
       <c r="S6">
-        <v>2.804</v>
+        <v>2.578</v>
       </c>
       <c r="T6">
-        <v>5.05</v>
+        <v>5.225</v>
       </c>
       <c r="U6">
-        <v>5.072</v>
+        <v>3.524</v>
       </c>
       <c r="V6">
-        <v>2.059</v>
+        <v>1.99</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>0.737</v>
       </c>
       <c r="X6">
-        <v>0.391</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7">
-        <v>823144</v>
+        <v>823067</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1133,7 +1184,7 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>676106</v>
+        <v>808963</v>
       </c>
       <c r="E7" t="s">
         <v>48</v>
@@ -1145,7 +1196,7 @@
         <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
         <v>47</v>
@@ -1154,51 +1205,51 @@
         <v>46</v>
       </c>
       <c r="K7">
-        <v>19.799</v>
+        <v>18.559</v>
       </c>
       <c r="L7">
-        <v>4.844</v>
+        <v>4.292</v>
       </c>
       <c r="M7">
-        <v>0.279</v>
+        <v>0.119</v>
       </c>
       <c r="N7">
-        <v>0.211</v>
+        <v>0.231</v>
       </c>
       <c r="O7">
-        <v>0.511</v>
+        <v>0.65</v>
       </c>
       <c r="P7">
-        <v>0.184</v>
+        <v>0.068</v>
       </c>
       <c r="Q7">
-        <v>13.344</v>
+        <v>9.461</v>
       </c>
       <c r="R7">
-        <v>23.805</v>
+        <v>18.187</v>
       </c>
       <c r="S7">
-        <v>1.746</v>
+        <v>1.86</v>
       </c>
       <c r="T7">
-        <v>3.925</v>
+        <v>3.466</v>
       </c>
       <c r="U7">
-        <v>4.035</v>
+        <v>3.302</v>
       </c>
       <c r="V7">
-        <v>1.485</v>
+        <v>2.459</v>
       </c>
       <c r="W7">
-        <v>0.566</v>
+        <v>0.374</v>
       </c>
       <c r="X7">
-        <v>0.483</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8">
-        <v>823308</v>
+        <v>823144</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1207,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="D8">
-        <v>650633</v>
+        <v>607625</v>
       </c>
       <c r="E8" t="s">
         <v>51</v>
@@ -1219,7 +1270,7 @@
         <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
         <v>53</v>
@@ -1228,51 +1279,51 @@
         <v>54</v>
       </c>
       <c r="K8">
-        <v>22.085</v>
+        <v>22.924</v>
       </c>
       <c r="L8">
-        <v>5.134</v>
+        <v>5.276</v>
       </c>
       <c r="M8">
-        <v>0.311</v>
+        <v>0.159</v>
       </c>
       <c r="N8">
-        <v>0.248</v>
+        <v>0.434</v>
       </c>
       <c r="O8">
-        <v>0.442</v>
+        <v>0.407</v>
       </c>
       <c r="P8">
-        <v>0.303</v>
+        <v>0.334</v>
       </c>
       <c r="Q8">
-        <v>15.042</v>
+        <v>12.3</v>
       </c>
       <c r="R8">
-        <v>27.963</v>
+        <v>24.365</v>
       </c>
       <c r="S8">
-        <v>2.171</v>
+        <v>2.928</v>
       </c>
       <c r="T8">
-        <v>3.99</v>
+        <v>5.225</v>
       </c>
       <c r="U8">
-        <v>5.333</v>
+        <v>5.011</v>
       </c>
       <c r="V8">
-        <v>2.832</v>
+        <v>2.073</v>
       </c>
       <c r="W8">
-        <v>0.65</v>
+        <v>1.117</v>
       </c>
       <c r="X8">
-        <v>0.165</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9">
-        <v>823308</v>
+        <v>823144</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1281,7 +1332,7 @@
         <v>50</v>
       </c>
       <c r="D9">
-        <v>680732</v>
+        <v>676106</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -1293,7 +1344,7 @@
         <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I9" t="s">
         <v>54</v>
@@ -1302,66 +1353,66 @@
         <v>53</v>
       </c>
       <c r="K9">
-        <v>21.242</v>
+        <v>19.936</v>
       </c>
       <c r="L9">
-        <v>4.854</v>
+        <v>4.834</v>
       </c>
       <c r="M9">
-        <v>0.144</v>
+        <v>0.276</v>
       </c>
       <c r="N9">
-        <v>0.377</v>
+        <v>0.224</v>
       </c>
       <c r="O9">
-        <v>0.479</v>
+        <v>0.501</v>
       </c>
       <c r="P9">
-        <v>0.204</v>
+        <v>0.18</v>
       </c>
       <c r="Q9">
-        <v>11.548</v>
+        <v>13.021</v>
       </c>
       <c r="R9">
-        <v>22.457</v>
+        <v>23.466</v>
       </c>
       <c r="S9">
-        <v>2.543</v>
+        <v>1.913</v>
       </c>
       <c r="T9">
-        <v>4.91</v>
+        <v>4.128</v>
       </c>
       <c r="U9">
-        <v>4.613</v>
+        <v>4.109</v>
       </c>
       <c r="V9">
-        <v>1.911</v>
+        <v>1.471</v>
       </c>
       <c r="W9">
-        <v>0.723</v>
+        <v>0.625</v>
       </c>
       <c r="X9">
-        <v>0.457</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10">
-        <v>823388</v>
+        <v>823308</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>669387</v>
+        <v>650633</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -1370,72 +1421,72 @@
         <v>29</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K10">
-        <v>19.694</v>
+        <v>22.109</v>
       </c>
       <c r="L10">
-        <v>4.677</v>
+        <v>5.145</v>
       </c>
       <c r="M10">
-        <v>0.24</v>
+        <v>0.304</v>
       </c>
       <c r="N10">
-        <v>0.21</v>
+        <v>0.225</v>
       </c>
       <c r="O10">
-        <v>0.55</v>
+        <v>0.471</v>
       </c>
       <c r="P10">
-        <v>0.156</v>
+        <v>0.3</v>
       </c>
       <c r="Q10">
-        <v>14.706</v>
+        <v>15.166</v>
       </c>
       <c r="R10">
-        <v>26.229</v>
+        <v>28.127</v>
       </c>
       <c r="S10">
-        <v>1.729</v>
+        <v>2.167</v>
       </c>
       <c r="T10">
-        <v>4.09</v>
+        <v>4.021</v>
       </c>
       <c r="U10">
-        <v>5.107</v>
+        <v>5.39</v>
       </c>
       <c r="V10">
-        <v>1.798</v>
+        <v>2.776</v>
       </c>
       <c r="W10">
-        <v>0.347</v>
+        <v>0.664</v>
       </c>
       <c r="X10">
-        <v>0.49</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11">
-        <v>823388</v>
+        <v>823308</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>695076</v>
+        <v>680732</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
@@ -1444,66 +1495,66 @@
         <v>34</v>
       </c>
       <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
         <v>60</v>
       </c>
-      <c r="J11" t="s">
-        <v>59</v>
-      </c>
       <c r="K11">
-        <v>22.14</v>
+        <v>21.202</v>
       </c>
       <c r="L11">
-        <v>5.024</v>
+        <v>4.843</v>
       </c>
       <c r="M11">
-        <v>0.164</v>
+        <v>0.129</v>
       </c>
       <c r="N11">
-        <v>0.395</v>
+        <v>0.373</v>
       </c>
       <c r="O11">
-        <v>0.441</v>
+        <v>0.498</v>
       </c>
       <c r="P11">
-        <v>0.271</v>
+        <v>0.216</v>
       </c>
       <c r="Q11">
-        <v>10.616</v>
+        <v>11.081</v>
       </c>
       <c r="R11">
-        <v>21.684</v>
+        <v>21.835</v>
       </c>
       <c r="S11">
-        <v>2.555</v>
+        <v>2.621</v>
       </c>
       <c r="T11">
-        <v>5.13</v>
+        <v>4.93</v>
       </c>
       <c r="U11">
-        <v>4.069</v>
+        <v>4.51</v>
       </c>
       <c r="V11">
-        <v>2.169</v>
+        <v>1.927</v>
       </c>
       <c r="W11">
-        <v>0.528</v>
+        <v>0.757</v>
       </c>
       <c r="X11">
-        <v>0.441</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12">
-        <v>823715</v>
+        <v>823388</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>656302</v>
+        <v>669387</v>
       </c>
       <c r="E12" t="s">
         <v>64</v>
@@ -1515,7 +1566,7 @@
         <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I12" t="s">
         <v>66</v>
@@ -1524,60 +1575,60 @@
         <v>67</v>
       </c>
       <c r="K12">
-        <v>22.018</v>
+        <v>19.654</v>
       </c>
       <c r="L12">
-        <v>4.892</v>
+        <v>4.646</v>
       </c>
       <c r="M12">
-        <v>0.171</v>
+        <v>0.244</v>
       </c>
       <c r="N12">
-        <v>0.338</v>
+        <v>0.209</v>
       </c>
       <c r="O12">
-        <v>0.492</v>
+        <v>0.547</v>
       </c>
       <c r="P12">
-        <v>0.235</v>
+        <v>0.148</v>
       </c>
       <c r="Q12">
-        <v>16.356</v>
+        <v>14.758</v>
       </c>
       <c r="R12">
-        <v>30.346</v>
+        <v>26.295</v>
       </c>
       <c r="S12">
-        <v>2.385</v>
+        <v>1.736</v>
       </c>
       <c r="T12">
-        <v>4.445</v>
+        <v>4.093</v>
       </c>
       <c r="U12">
-        <v>6.954</v>
+        <v>5.17</v>
       </c>
       <c r="V12">
-        <v>3.009</v>
+        <v>1.806</v>
       </c>
       <c r="W12">
-        <v>0.543</v>
+        <v>0.341</v>
       </c>
       <c r="X12">
-        <v>0.406</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13">
-        <v>823715</v>
+        <v>823388</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>687570</v>
+        <v>695076</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -1586,10 +1637,10 @@
         <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
         <v>67</v>
@@ -1598,51 +1649,51 @@
         <v>66</v>
       </c>
       <c r="K13">
-        <v>21.319</v>
+        <v>22.368</v>
       </c>
       <c r="L13">
-        <v>5.109</v>
+        <v>5.016</v>
       </c>
       <c r="M13">
-        <v>0.275</v>
+        <v>0.166</v>
       </c>
       <c r="N13">
-        <v>0.265</v>
+        <v>0.392</v>
       </c>
       <c r="O13">
-        <v>0.46</v>
+        <v>0.442</v>
       </c>
       <c r="P13">
-        <v>0.3</v>
+        <v>0.264</v>
       </c>
       <c r="Q13">
-        <v>15.235</v>
+        <v>10.099</v>
       </c>
       <c r="R13">
-        <v>27.592</v>
+        <v>21.125</v>
       </c>
       <c r="S13">
-        <v>1.91</v>
+        <v>2.703</v>
       </c>
       <c r="T13">
-        <v>3.949</v>
+        <v>5.359</v>
       </c>
       <c r="U13">
-        <v>5.049</v>
+        <v>4.044</v>
       </c>
       <c r="V13">
-        <v>2.114</v>
+        <v>2.207</v>
       </c>
       <c r="W13">
-        <v>0.628</v>
+        <v>0.569</v>
       </c>
       <c r="X13">
-        <v>0.322</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14">
-        <v>823876</v>
+        <v>823554</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1651,7 +1702,7 @@
         <v>70</v>
       </c>
       <c r="D14">
-        <v>676974</v>
+        <v>677960</v>
       </c>
       <c r="E14" t="s">
         <v>71</v>
@@ -1660,7 +1711,7 @@
         <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
@@ -1672,140 +1723,140 @@
         <v>74</v>
       </c>
       <c r="K14">
-        <v>22.406</v>
+        <v>22.58</v>
       </c>
       <c r="L14">
-        <v>5.263</v>
+        <v>5.257</v>
       </c>
       <c r="M14">
-        <v>0.239</v>
+        <v>0.301</v>
       </c>
       <c r="N14">
-        <v>0.348</v>
+        <v>0.278</v>
       </c>
       <c r="O14">
-        <v>0.413</v>
+        <v>0.421</v>
       </c>
       <c r="P14">
-        <v>0.335</v>
+        <v>0.339</v>
       </c>
       <c r="Q14">
-        <v>13.154</v>
+        <v>16.574</v>
       </c>
       <c r="R14">
-        <v>25.246</v>
+        <v>30.475</v>
       </c>
       <c r="S14">
-        <v>2.254</v>
+        <v>2.271</v>
       </c>
       <c r="T14">
-        <v>4.808</v>
+        <v>4.988</v>
       </c>
       <c r="U14">
-        <v>4.481</v>
+        <v>6.119</v>
       </c>
       <c r="V14">
-        <v>2.048</v>
+        <v>1.955</v>
       </c>
       <c r="W14">
-        <v>0.502</v>
+        <v>0.662</v>
       </c>
       <c r="X14">
-        <v>0.627</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>824042</v>
+        <v>823554</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>680694</v>
+      </c>
+      <c r="E15" t="s">
         <v>75</v>
       </c>
-      <c r="D15">
-        <v>672282</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>76</v>
       </c>
-      <c r="F15" t="s">
-        <v>77</v>
-      </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K15">
-        <v>23.434</v>
+        <v>22.203</v>
       </c>
       <c r="L15">
-        <v>5.689</v>
+        <v>4.908</v>
       </c>
       <c r="M15">
-        <v>0.236</v>
+        <v>0.164</v>
       </c>
       <c r="N15">
-        <v>0.336</v>
+        <v>0.358</v>
       </c>
       <c r="O15">
-        <v>0.428</v>
+        <v>0.477</v>
       </c>
       <c r="P15">
-        <v>0.372</v>
+        <v>0.231</v>
       </c>
       <c r="Q15">
-        <v>19.457</v>
+        <v>14.06</v>
       </c>
       <c r="R15">
-        <v>34.222</v>
+        <v>27.084</v>
       </c>
       <c r="S15">
-        <v>2.172</v>
+        <v>2.59</v>
       </c>
       <c r="T15">
-        <v>4.845</v>
+        <v>4.397</v>
       </c>
       <c r="U15">
-        <v>6.923</v>
+        <v>6.073</v>
       </c>
       <c r="V15">
-        <v>1.664</v>
+        <v>3.283</v>
       </c>
       <c r="W15">
-        <v>0.706</v>
+        <v>0.648</v>
       </c>
       <c r="X15">
-        <v>0.392</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>824042</v>
+        <v>823715</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D16">
-        <v>690997</v>
+        <v>656302</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
@@ -1814,66 +1865,66 @@
         <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K16">
-        <v>22.748</v>
+        <v>22.019</v>
       </c>
       <c r="L16">
-        <v>5.485</v>
+        <v>4.839</v>
       </c>
       <c r="M16">
-        <v>0.244</v>
+        <v>0.159</v>
       </c>
       <c r="N16">
-        <v>0.263</v>
+        <v>0.364</v>
       </c>
       <c r="O16">
-        <v>0.493</v>
+        <v>0.477</v>
       </c>
       <c r="P16">
-        <v>0.428</v>
+        <v>0.226</v>
       </c>
       <c r="Q16">
-        <v>21.548</v>
+        <v>15.269</v>
       </c>
       <c r="R16">
-        <v>37.801</v>
+        <v>28.867</v>
       </c>
       <c r="S16">
-        <v>1.863</v>
+        <v>2.431</v>
       </c>
       <c r="T16">
-        <v>3.916</v>
+        <v>4.539</v>
       </c>
       <c r="U16">
-        <v>7.92</v>
+        <v>6.595</v>
       </c>
       <c r="V16">
-        <v>2.574</v>
+        <v>3.099</v>
       </c>
       <c r="W16">
-        <v>0.494</v>
+        <v>0.523</v>
       </c>
       <c r="X16">
-        <v>0.346</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>824284</v>
+        <v>823715</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>672456</v>
+        <v>687570</v>
       </c>
       <c r="E17" t="s">
         <v>82</v>
@@ -1882,146 +1933,146 @@
         <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>22.248</v>
+        <v>21.218</v>
       </c>
       <c r="L17">
-        <v>5.249</v>
+        <v>5.105</v>
       </c>
       <c r="M17">
-        <v>0.312</v>
+        <v>0.296</v>
       </c>
       <c r="N17">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="O17">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="P17">
-        <v>0.32</v>
+        <v>0.287</v>
       </c>
       <c r="Q17">
-        <v>13.72</v>
+        <v>15.32</v>
       </c>
       <c r="R17">
-        <v>25.8</v>
+        <v>27.579</v>
       </c>
       <c r="S17">
-        <v>2.188</v>
+        <v>1.865</v>
       </c>
       <c r="T17">
-        <v>4.833</v>
+        <v>3.903</v>
       </c>
       <c r="U17">
-        <v>4.488</v>
+        <v>4.977</v>
       </c>
       <c r="V17">
-        <v>1.754</v>
+        <v>2.07</v>
       </c>
       <c r="W17">
-        <v>0.51</v>
+        <v>0.597</v>
       </c>
       <c r="X17">
-        <v>0.294</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>824284</v>
+        <v>823876</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="D18">
-        <v>677958</v>
+        <v>676974</v>
       </c>
       <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
         <v>86</v>
-      </c>
-      <c r="F18" t="s">
-        <v>87</v>
       </c>
       <c r="G18" t="s">
         <v>38</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K18">
-        <v>21.683</v>
+        <v>22.931</v>
       </c>
       <c r="L18">
-        <v>4.801</v>
+        <v>5.352</v>
       </c>
       <c r="M18">
-        <v>0.148</v>
+        <v>0.253</v>
       </c>
       <c r="N18">
-        <v>0.372</v>
+        <v>0.34</v>
       </c>
       <c r="O18">
-        <v>0.48</v>
+        <v>0.407</v>
       </c>
       <c r="P18">
-        <v>0.217</v>
+        <v>0.354</v>
       </c>
       <c r="Q18">
-        <v>8.31</v>
+        <v>13.105</v>
       </c>
       <c r="R18">
-        <v>18.371</v>
+        <v>25.447</v>
       </c>
       <c r="S18">
-        <v>2.654</v>
+        <v>2.33</v>
       </c>
       <c r="T18">
-        <v>4.95</v>
+        <v>5.031</v>
       </c>
       <c r="U18">
-        <v>3.391</v>
+        <v>4.482</v>
       </c>
       <c r="V18">
-        <v>2.651</v>
+        <v>2.077</v>
       </c>
       <c r="W18">
-        <v>0.47</v>
+        <v>0.488</v>
       </c>
       <c r="X18">
-        <v>0.279</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>824685</v>
+        <v>823876</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D19">
-        <v>669194</v>
+        <v>691725</v>
       </c>
       <c r="E19" t="s">
         <v>89</v>
@@ -2036,72 +2087,72 @@
         <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K19">
-        <v>22.339</v>
+        <v>21.894</v>
       </c>
       <c r="L19">
-        <v>5.038</v>
+        <v>5.119</v>
       </c>
       <c r="M19">
-        <v>0.153</v>
+        <v>0.2</v>
       </c>
       <c r="N19">
-        <v>0.386</v>
+        <v>0.283</v>
       </c>
       <c r="O19">
-        <v>0.461</v>
+        <v>0.517</v>
       </c>
       <c r="P19">
-        <v>0.273</v>
+        <v>0.298</v>
       </c>
       <c r="Q19">
-        <v>10.346</v>
+        <v>12.227</v>
       </c>
       <c r="R19">
-        <v>21.491</v>
+        <v>23.703</v>
       </c>
       <c r="S19">
-        <v>2.507</v>
+        <v>2.122</v>
       </c>
       <c r="T19">
-        <v>5.089</v>
+        <v>4.586</v>
       </c>
       <c r="U19">
-        <v>3.965</v>
+        <v>4.106</v>
       </c>
       <c r="V19">
-        <v>2.439</v>
+        <v>2.19</v>
       </c>
       <c r="W19">
-        <v>0.456</v>
+        <v>0.438</v>
       </c>
       <c r="X19">
-        <v>0.336</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
-        <v>824685</v>
+        <v>824042</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D20">
-        <v>684007</v>
+        <v>672282</v>
       </c>
       <c r="E20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
         <v>93</v>
-      </c>
-      <c r="F20" t="s">
-        <v>94</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -2110,72 +2161,72 @@
         <v>29</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K20">
-        <v>23.216</v>
+        <v>23.516</v>
       </c>
       <c r="L20">
-        <v>5.691</v>
+        <v>5.675</v>
       </c>
       <c r="M20">
-        <v>0.357</v>
+        <v>0.243</v>
       </c>
       <c r="N20">
-        <v>0.241</v>
+        <v>0.352</v>
       </c>
       <c r="O20">
-        <v>0.402</v>
+        <v>0.405</v>
       </c>
       <c r="P20">
-        <v>0.452</v>
+        <v>0.361</v>
       </c>
       <c r="Q20">
-        <v>16.087</v>
+        <v>18.897</v>
       </c>
       <c r="R20">
-        <v>29.367</v>
+        <v>33.465</v>
       </c>
       <c r="S20">
-        <v>2.029</v>
+        <v>2.325</v>
       </c>
       <c r="T20">
-        <v>4.673</v>
+        <v>4.967</v>
       </c>
       <c r="U20">
-        <v>4.809</v>
+        <v>6.838</v>
       </c>
       <c r="V20">
-        <v>1.573</v>
+        <v>1.662</v>
       </c>
       <c r="W20">
-        <v>0.63</v>
+        <v>0.773</v>
       </c>
       <c r="X20">
-        <v>0.322</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21">
-        <v>824771</v>
+        <v>824042</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D21">
-        <v>681293</v>
+        <v>690997</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
         <v>38</v>
@@ -2184,146 +2235,146 @@
         <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K21">
-        <v>22.474</v>
+        <v>22.794</v>
       </c>
       <c r="L21">
-        <v>4.901</v>
+        <v>5.47</v>
       </c>
       <c r="M21">
-        <v>0.155</v>
+        <v>0.238</v>
       </c>
       <c r="N21">
-        <v>0.366</v>
+        <v>0.254</v>
       </c>
       <c r="O21">
-        <v>0.479</v>
+        <v>0.508</v>
       </c>
       <c r="P21">
-        <v>0.23</v>
+        <v>0.404</v>
       </c>
       <c r="Q21">
-        <v>10.306</v>
+        <v>21.254</v>
       </c>
       <c r="R21">
-        <v>21.771</v>
+        <v>37.28</v>
       </c>
       <c r="S21">
-        <v>3.035</v>
+        <v>1.926</v>
       </c>
       <c r="T21">
-        <v>5.221</v>
+        <v>3.972</v>
       </c>
       <c r="U21">
-        <v>4.775</v>
+        <v>7.868</v>
       </c>
       <c r="V21">
-        <v>2.817</v>
+        <v>2.56</v>
       </c>
       <c r="W21">
-        <v>0.717</v>
+        <v>0.511</v>
       </c>
       <c r="X21">
-        <v>1.124</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="22" spans="1:24">
       <c r="A22">
-        <v>824771</v>
+        <v>824284</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="D22">
-        <v>813349</v>
+        <v>672456</v>
       </c>
       <c r="E22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="F22" t="s">
-        <v>100</v>
-      </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K22">
-        <v>22.41</v>
+        <v>22.742</v>
       </c>
       <c r="L22">
-        <v>5.235</v>
+        <v>5.389</v>
       </c>
       <c r="M22">
-        <v>0.314</v>
+        <v>0.342</v>
       </c>
       <c r="N22">
-        <v>0.253</v>
+        <v>0.231</v>
       </c>
       <c r="O22">
-        <v>0.433</v>
+        <v>0.427</v>
       </c>
       <c r="P22">
-        <v>0.32</v>
+        <v>0.363</v>
       </c>
       <c r="Q22">
-        <v>13.131</v>
+        <v>14.09</v>
       </c>
       <c r="R22">
-        <v>25.26</v>
+        <v>26.528</v>
       </c>
       <c r="S22">
-        <v>2.423</v>
+        <v>2.259</v>
       </c>
       <c r="T22">
-        <v>4.713</v>
+        <v>4.92</v>
       </c>
       <c r="U22">
-        <v>4.555</v>
+        <v>4.544</v>
       </c>
       <c r="V22">
-        <v>2.244</v>
+        <v>1.738</v>
       </c>
       <c r="W22">
-        <v>0.715</v>
+        <v>0.541</v>
       </c>
       <c r="X22">
-        <v>0.167</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="23" spans="1:24">
       <c r="A23">
-        <v>825014</v>
+        <v>824284</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D23">
-        <v>677944</v>
+        <v>677958</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
@@ -2332,49 +2383,49 @@
         <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>21.42</v>
+        <v>22.122</v>
       </c>
       <c r="L23">
-        <v>4.599</v>
+        <v>4.862</v>
       </c>
       <c r="M23">
-        <v>0.123</v>
+        <v>0.146</v>
       </c>
       <c r="N23">
-        <v>0.424</v>
+        <v>0.393</v>
       </c>
       <c r="O23">
-        <v>0.453</v>
+        <v>0.461</v>
       </c>
       <c r="P23">
-        <v>0.16</v>
+        <v>0.218</v>
       </c>
       <c r="Q23">
-        <v>6.316</v>
+        <v>7.906</v>
       </c>
       <c r="R23">
-        <v>15.428</v>
+        <v>17.953</v>
       </c>
       <c r="S23">
-        <v>3.418</v>
+        <v>2.859</v>
       </c>
       <c r="T23">
-        <v>5.775</v>
+        <v>5.15</v>
       </c>
       <c r="U23">
-        <v>3.502</v>
+        <v>3.398</v>
       </c>
       <c r="V23">
-        <v>2.048</v>
+        <v>2.677</v>
       </c>
       <c r="W23">
-        <v>1.117</v>
+        <v>0.541</v>
       </c>
       <c r="X23">
         <v>0.309</v>
@@ -2382,16 +2433,16 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24">
-        <v>825014</v>
+        <v>824365</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="D24">
-        <v>682052</v>
+        <v>519242</v>
       </c>
       <c r="E24" t="s">
         <v>105</v>
@@ -2403,55 +2454,425 @@
         <v>28</v>
       </c>
       <c r="H24" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24">
+        <v>23.12</v>
+      </c>
+      <c r="L24">
+        <v>5.522</v>
+      </c>
+      <c r="M24">
+        <v>0.259</v>
+      </c>
+      <c r="N24">
+        <v>0.208</v>
+      </c>
+      <c r="O24">
+        <v>0.533</v>
+      </c>
+      <c r="P24">
+        <v>0.417</v>
+      </c>
+      <c r="Q24">
+        <v>15.835</v>
+      </c>
+      <c r="R24">
+        <v>29.399</v>
+      </c>
+      <c r="S24">
+        <v>2.434</v>
+      </c>
+      <c r="T24">
+        <v>5.069</v>
+      </c>
+      <c r="U24">
+        <v>5.637</v>
+      </c>
+      <c r="V24">
+        <v>1.676</v>
+      </c>
+      <c r="W24">
+        <v>0.741</v>
+      </c>
+      <c r="X24">
+        <v>0.397</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25">
+        <v>824365</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25">
+        <v>801403</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" t="s">
         <v>29</v>
       </c>
-      <c r="I24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24">
-        <v>23.069</v>
-      </c>
-      <c r="L24">
-        <v>5.306</v>
-      </c>
-      <c r="M24">
-        <v>0.358</v>
-      </c>
-      <c r="N24">
-        <v>0.211</v>
-      </c>
-      <c r="O24">
-        <v>0.43</v>
-      </c>
-      <c r="P24">
+      <c r="I25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J25" t="s">
+        <v>107</v>
+      </c>
+      <c r="K25">
+        <v>22.464</v>
+      </c>
+      <c r="L25">
+        <v>5.058</v>
+      </c>
+      <c r="M25">
+        <v>0.172</v>
+      </c>
+      <c r="N25">
+        <v>0.408</v>
+      </c>
+      <c r="O25">
+        <v>0.42</v>
+      </c>
+      <c r="P25">
+        <v>0.271</v>
+      </c>
+      <c r="Q25">
+        <v>10.328</v>
+      </c>
+      <c r="R25">
+        <v>21.428</v>
+      </c>
+      <c r="S25">
+        <v>2.862</v>
+      </c>
+      <c r="T25">
+        <v>4.872</v>
+      </c>
+      <c r="U25">
+        <v>4.241</v>
+      </c>
+      <c r="V25">
+        <v>2.637</v>
+      </c>
+      <c r="W25">
+        <v>0.891</v>
+      </c>
+      <c r="X25">
+        <v>0.563</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26">
+        <v>824685</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26">
+        <v>669194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" t="s">
+        <v>115</v>
+      </c>
+      <c r="K26">
+        <v>22.572</v>
+      </c>
+      <c r="L26">
+        <v>5.131</v>
+      </c>
+      <c r="M26">
+        <v>0.166</v>
+      </c>
+      <c r="N26">
+        <v>0.37</v>
+      </c>
+      <c r="O26">
+        <v>0.464</v>
+      </c>
+      <c r="P26">
+        <v>0.316</v>
+      </c>
+      <c r="Q26">
+        <v>10.84</v>
+      </c>
+      <c r="R26">
+        <v>22.296</v>
+      </c>
+      <c r="S26">
+        <v>2.48</v>
+      </c>
+      <c r="T26">
+        <v>5.056</v>
+      </c>
+      <c r="U26">
+        <v>4.027</v>
+      </c>
+      <c r="V26">
+        <v>2.392</v>
+      </c>
+      <c r="W26">
+        <v>0.484</v>
+      </c>
+      <c r="X26">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27">
+        <v>824685</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27">
+        <v>684007</v>
+      </c>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>115</v>
+      </c>
+      <c r="J27" t="s">
+        <v>114</v>
+      </c>
+      <c r="K27">
+        <v>23.515</v>
+      </c>
+      <c r="L27">
+        <v>5.772</v>
+      </c>
+      <c r="M27">
+        <v>0.349</v>
+      </c>
+      <c r="N27">
+        <v>0.248</v>
+      </c>
+      <c r="O27">
+        <v>0.403</v>
+      </c>
+      <c r="P27">
+        <v>0.482</v>
+      </c>
+      <c r="Q27">
+        <v>15.85</v>
+      </c>
+      <c r="R27">
+        <v>29.15</v>
+      </c>
+      <c r="S27">
+        <v>2.073</v>
+      </c>
+      <c r="T27">
+        <v>4.699</v>
+      </c>
+      <c r="U27">
+        <v>4.676</v>
+      </c>
+      <c r="V27">
+        <v>1.606</v>
+      </c>
+      <c r="W27">
+        <v>0.661</v>
+      </c>
+      <c r="X27">
         <v>0.342</v>
       </c>
-      <c r="Q24">
-        <v>13.797</v>
-      </c>
-      <c r="R24">
-        <v>26.613</v>
-      </c>
-      <c r="S24">
-        <v>2.547</v>
-      </c>
-      <c r="T24">
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28">
+        <v>824771</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28">
+        <v>681293</v>
+      </c>
+      <c r="E28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" t="s">
+        <v>120</v>
+      </c>
+      <c r="J28" t="s">
+        <v>121</v>
+      </c>
+      <c r="K28">
+        <v>22.383</v>
+      </c>
+      <c r="L28">
+        <v>4.892</v>
+      </c>
+      <c r="M28">
+        <v>0.152</v>
+      </c>
+      <c r="N28">
+        <v>0.394</v>
+      </c>
+      <c r="O28">
+        <v>0.454</v>
+      </c>
+      <c r="P28">
+        <v>0.23</v>
+      </c>
+      <c r="Q28">
+        <v>10.229</v>
+      </c>
+      <c r="R28">
+        <v>21.62</v>
+      </c>
+      <c r="S28">
+        <v>3.061</v>
+      </c>
+      <c r="T28">
+        <v>5.251</v>
+      </c>
+      <c r="U28">
+        <v>4.767</v>
+      </c>
+      <c r="V28">
+        <v>2.751</v>
+      </c>
+      <c r="W28">
+        <v>0.701</v>
+      </c>
+      <c r="X28">
+        <v>1.146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29">
+        <v>824771</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29">
+        <v>813349</v>
+      </c>
+      <c r="E29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K29">
+        <v>22.758</v>
+      </c>
+      <c r="L29">
+        <v>5.324</v>
+      </c>
+      <c r="M29">
+        <v>0.34</v>
+      </c>
+      <c r="N29">
+        <v>0.249</v>
+      </c>
+      <c r="O29">
+        <v>0.41</v>
+      </c>
+      <c r="P29">
+        <v>0.341</v>
+      </c>
+      <c r="Q29">
+        <v>13.833</v>
+      </c>
+      <c r="R29">
+        <v>26.396</v>
+      </c>
+      <c r="S29">
+        <v>2.411</v>
+      </c>
+      <c r="T29">
         <v>4.769</v>
       </c>
-      <c r="U24">
-        <v>4.939</v>
-      </c>
-      <c r="V24">
-        <v>2.516</v>
-      </c>
-      <c r="W24">
-        <v>0.738</v>
-      </c>
-      <c r="X24">
-        <v>0.503</v>
+      <c r="U29">
+        <v>4.75</v>
+      </c>
+      <c r="V29">
+        <v>2.239</v>
+      </c>
+      <c r="W29">
+        <v>0.716</v>
+      </c>
+      <c r="X29">
+        <v>0.188</v>
       </c>
     </row>
   </sheetData>
